--- a/stories/arbres/ATOM-AUT.ROU.001-06.xlsx
+++ b/stories/arbres/ATOM-AUT.ROU.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le matin, Bénédicte ouvre les yeux. Maman dit : une étape après l'autre. D'abord, Bénédicte se lève. Ses pieds touchent le tapis. Ensuite, elle s'habille. Elle met le pull. Elle met le pantalon. Papa dit : maintenant, le déjeuner. Bénédicte s'assoit. Elle mange du pain. Elle boit du lait. Maman dit : ensuite, le sac. Bénédicte met la gourde. Elle met le cahier. Une étape après l'autre. Bénédicte est prête.</t>
+          <t>Le matin, Bénédicte ouvre les yeux. Une étape après l'autre. D'abord, Bénédicte se lève. Ses pieds touchent le tapis. Ensuite, elle s'habille. Elle met le pull. Elle met le pantalon. Maintenant, le déjeuner. Bénédicte s'assoit. Elle mange du pain. Elle boit du lait. Ensuite, le sac. Bénédicte met la gourde. Elle met le cahier. Une étape après l'autre. Bénédicte est prête.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Le matin, Bénédicte ouvre les yeux.
+maman|Une étape après l'autre. D'abord, Bénédicte se lève. Ses pieds touchent le tapis. Ensuite, elle s'habille.
+narrateur|Elle met le pull. Elle met le pantalon.
+papa|Maintenant, le déjeuner.
+narrateur|Bénédicte s'assoit. Elle mange du pain. Elle boit du lait.
+maman|Ensuite, le sac.
+narrateur|Bénédicte met la gourde. Elle met le cahier. Une étape après l'autre. Bénédicte est prête.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Bénédicte se prépare. Comment avance-t-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Bénédicte a fait l'étape dite. Se lever. S'habiller. Déjeuner. Le sac. Une étape après l'autre.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1828,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Bénédicte met les chaussures. Maman ouvre la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1995,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.ROU.001-06.xlsx
+++ b/stories/arbres/ATOM-AUT.ROU.001-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 narrateur|Bénédicte met la gourde. Elle met le cahier. Une étape après l'autre. Bénédicte est prête.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Bénédicte se prépare. Comment avance-t-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1677,7 @@
           <t>narrateur|Bénédicte a fait l'étape dite. Se lever. S'habiller. Déjeuner. Le sac. Une étape après l'autre.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1841,7 @@
           <t>narrateur|Bénédicte met les chaussures. Maman ouvre la porte.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2009,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2052,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2267,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-AUT.ROU.001-06.xlsx
+++ b/stories/arbres/ATOM-AUT.ROU.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bénédicte, une étape après l'autre</t>
+          <t>Le doudou de Mila</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le doudou rouge attend sur la chaise. Mila se prépare, une étape après l'autre, pour le mettre dans le sac.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le matin, Bénédicte ouvre les yeux. Une étape après l'autre. D'abord, Bénédicte se lève. Ses pieds touchent le tapis. Ensuite, elle s'habille. Elle met le pull. Elle met le pantalon. Maintenant, le déjeuner. Bénédicte s'assoit. Elle mange du pain. Elle boit du lait. Ensuite, le sac. Bénédicte met la gourde. Elle met le cahier. Une étape après l'autre. Bénédicte est prête.</t>
+          <t>La chambre de Mila est petite. Les murs sont couleur pêche. Papa et maman sont dans la maison. Sur la chaise, un doudou rouge attend. Il a deux oreilles toutes molles. Il a un nez en fil. Mila, tu vois le doudou ? Oui, maman. Il attend. Il t'attend pour le sac. En ce moment, Mila ouvre les yeux. Le drap est chaud. Ça sent le doudou. On se lève. Une étape après l'autre. Mila se lève. Ses pieds touchent le tapis. Le tapis est doux. Bravo. Tu es debout. Tu as fait l'étape dite. Ensuite, on s'habille. Le pull rose est sur le lit. Mila met le pull. Elle met le pantalon. Elle met les chaussettes. C'est fait. Bravo, Mila. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1324,40 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Le matin, Bénédicte ouvre les yeux.
-maman|Une étape après l'autre. D'abord, Bénédicte se lève. Ses pieds touchent le tapis. Ensuite, elle s'habille.
-narrateur|Elle met le pull. Elle met le pantalon.
-papa|Maintenant, le déjeuner.
-narrateur|Bénédicte s'assoit. Elle mange du pain. Elle boit du lait.
-maman|Ensuite, le sac.
-narrateur|Bénédicte met la gourde. Elle met le cahier. Une étape après l'autre. Bénédicte est prête.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|La chambre de Mila est petite.
+narrateur|Les murs sont couleur pêche.
+narrateur|Papa et maman sont dans la maison.
+narrateur|Sur la chaise, un doudou rouge attend.
+narrateur|Il a deux oreilles toutes molles.
+narrateur|Il a un nez en fil.
+maman|Mila, tu vois le doudou ?
+enfant-f|Oui, maman. Il attend.
+papa|Il t'attend pour le sac.
+narrateur|En ce moment, Mila ouvre les yeux.
+narrateur|Le drap est chaud.
+narrateur|Ça sent le doudou.
+papa|On se lève.
+papa|Une étape après l'autre.
+narrateur|Mila se lève.
+narrateur|Ses pieds touchent le tapis.
+narrateur|Le tapis est doux.
+maman|Bravo. Tu es debout.
+maman|Tu as fait l'étape dite.
+papa|Ensuite, on s'habille.
+narrateur|Le pull rose est sur le lit.
+narrateur|Mila met le pull.
+narrateur|Elle met le pantalon.
+narrateur|Elle met les chaussettes.
+enfant-f|C'est fait.
+papa|Bravo, Mila.
+papa|Tu as fait du bon travail.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>doudou</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1346,7 +1382,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Bénédicte se prépare. Comment avance-t-elle ?</t>
+          <t>Mila se prépare. Comment avance-t-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,7 +1538,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Bénédicte se prépare. Comment avance-t-elle ?</t>
+          <t>narrateur|Mila se prépare.
+narrateur|Comment avance-t-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1530,7 +1567,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Bénédicte a fait l'étape dite. Se lever. S'habiller. Déjeuner. Le sac. Une étape après l'autre.</t>
+          <t>Mila a fait l'étape dite. Une étape après l'autre. Maintenant, le déjeuner. Mila va à la cuisine. La table est ronde. Il y a du pain. Il y a une pomme coupée. Mila s'assoit. Tu es bien assise. Bravo. Elle mange du pain. Elle boit du lait. Tu as fini ton bol ? Oui, papa. Bravo. L'étape est finie.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1674,7 +1711,20 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Bénédicte a fait l'étape dite. Se lever. S'habiller. Déjeuner. Le sac. Une étape après l'autre.</t>
+          <t>narrateur|Mila a fait l'étape dite.
+maman|Une étape après l'autre.
+papa|Maintenant, le déjeuner.
+narrateur|Mila va à la cuisine.
+narrateur|La table est ronde.
+narrateur|Il y a du pain.
+narrateur|Il y a une pomme coupée.
+narrateur|Mila s'assoit.
+maman|Tu es bien assise. Bravo.
+narrateur|Elle mange du pain.
+narrateur|Elle boit du lait.
+papa|Tu as fini ton bol ?
+enfant-f|Oui, papa.
+papa|Bravo. L'étape est finie.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1702,7 +1752,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Bénédicte met les chaussures. Maman ouvre la porte.</t>
+          <t>Ensuite, le sac. Le sac rose est près de la chaise. Mila met la gourde. Elle met le cahier. Elle met le doudou rouge. Tu as mis ce que maman a dit. Le doudou est dans le sac. Bravo. Tu as fait du bon travail. Mila met les chaussures. Maman ouvre la porte. On est prêtes. Oui. Tu as enchaîné le matin. Une étape après l'autre.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1838,10 +1888,26 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Bénédicte met les chaussures. Maman ouvre la porte.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>maman|Ensuite, le sac.
+narrateur|Le sac rose est près de la chaise.
+narrateur|Mila met la gourde.
+narrateur|Elle met le cahier.
+narrateur|Elle met le doudou rouge.
+papa|Tu as mis ce que maman a dit.
+enfant-f|Le doudou est dans le sac.
+maman|Bravo. Tu as fait du bon travail.
+narrateur|Mila met les chaussures.
+narrateur|Maman ouvre la porte.
+enfant-f|On est prêtes.
+maman|Oui. Tu as enchaîné le matin.
+papa|Une étape après l'autre.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>porte</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1866,7 +1932,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Je me suis levée. Je me suis habillée. J'ai déjeuné. J'ai mis le doudou. Bravo, Mila. Le doudou n'a plus besoin d'attendre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2006,7 +2072,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|Je me suis levée.
+enfant-f|Je me suis habillée.
+enfant-f|J'ai déjeuné.
+enfant-f|J'ai mis le doudou.
+maman|Bravo, Mila.
+papa|Le doudou n'a plus besoin d'attendre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2028,7 +2100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2066,6 +2138,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.ROU.001-06.xlsx
+++ b/stories/arbres/ATOM-AUT.ROU.001-06.xlsx
@@ -1184,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La chambre de Mila est petite. Les murs sont couleur pêche. Papa et maman sont dans la maison. Sur la chaise, un doudou rouge attend. Il a deux oreilles toutes molles. Il a un nez en fil. Mila, tu vois le doudou ? Oui, maman. Il attend. Il t'attend pour le sac. En ce moment, Mila ouvre les yeux. Le drap est chaud. Ça sent le doudou. On se lève. Une étape après l'autre. Mila se lève. Ses pieds touchent le tapis. Le tapis est doux. Bravo. Tu es debout. Tu as fait l'étape dite. Ensuite, on s'habille. Le pull rose est sur le lit. Mila met le pull. Elle met le pantalon. Elle met les chaussettes. C'est fait. Bravo, Mila. Tu as fait du bon travail.</t>
+          <t>Sur la chaise, un doudou rouge attend. Il a deux oreilles toutes molles. Il a un nez en fil. Une oreille penche un peu. L'autre oreille est droite. La chambre de Mila est petite. Les murs sont couleur pêche. Un mobile tourne très lentement. Papa et maman sont dans la maison. Mila, tu vois le doudou ? Oui, maman. Il attend. Il t'attend pour le sac. En ce moment, Mila ouvre les yeux. Le drap est chaud. Ça sent le doudou. Je veux le doudou. D'abord on se lève. Le doudou t'attend pour le sac. Mila regarde la chaise. Le doudou ne bouge pas. On se lève. Une étape après l'autre. Mila se lève. Ses pieds touchent le tapis. Le tapis est doux. Bravo. Tu es debout. Tu as fait l'étape dite. Ensuite, on s'habille. Le pull rose est sur le lit. Mila met le pull. Elle met le pantalon. Elle met les chaussettes. C'est fait. Bravo, Mila. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1324,24 +1324,34 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|La chambre de Mila est petite.
-narrateur|Les murs sont couleur pêche.
-narrateur|Papa et maman sont dans la maison.
-narrateur|Sur la chaise, un doudou rouge attend.
+          <t>narrateur|Sur la chaise, un doudou rouge attend.
 narrateur|Il a deux oreilles toutes molles.
 narrateur|Il a un nez en fil.
+narrateur|Une oreille penche un peu.
+narrateur|L'autre oreille est droite.
+narrateur|La chambre de Mila est petite.
+narrateur|Les murs sont couleur pêche.
+narrateur|Un mobile tourne très lentement.
+narrateur|Papa et maman sont dans la maison.
 maman|Mila, tu vois le doudou ?
-enfant-f|Oui, maman. Il attend.
+enfant-f|Oui, maman.
+enfant-f|Il attend.
 papa|Il t'attend pour le sac.
 narrateur|En ce moment, Mila ouvre les yeux.
 narrateur|Le drap est chaud.
 narrateur|Ça sent le doudou.
+enfant-f|Je veux le doudou.
+maman|D'abord on se lève.
+maman|Le doudou t'attend pour le sac.
+narrateur|Mila regarde la chaise.
+narrateur|Le doudou ne bouge pas.
 papa|On se lève.
 papa|Une étape après l'autre.
 narrateur|Mila se lève.
 narrateur|Ses pieds touchent le tapis.
 narrateur|Le tapis est doux.
-maman|Bravo. Tu es debout.
+maman|Bravo.
+maman|Tu es debout.
 maman|Tu as fait l'étape dite.
 papa|Ensuite, on s'habille.
 narrateur|Le pull rose est sur le lit.
@@ -1567,7 +1577,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Mila a fait l'étape dite. Une étape après l'autre. Maintenant, le déjeuner. Mila va à la cuisine. La table est ronde. Il y a du pain. Il y a une pomme coupée. Mila s'assoit. Tu es bien assise. Bravo. Elle mange du pain. Elle boit du lait. Tu as fini ton bol ? Oui, papa. Bravo. L'étape est finie.</t>
+          <t>Mila a fait l'étape dite. Une étape après l'autre. Maintenant, le déjeuner. Mila va à la cuisine. La table est ronde. Il y a du pain. Il y a une pomme coupée. Tu veux un morceau de pomme ? Oui. Mila s'assoit. Tu es bien assise. Bravo. Elle mange du pain. Elle croque la pomme. La pomme est croquante. Elle est sucrée, la pomme ? Oui. Un peu. Elle boit du lait. Tu as fini ton bol ? Oui, papa. Bravo. L'étape est finie.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1718,13 +1728,22 @@
 narrateur|La table est ronde.
 narrateur|Il y a du pain.
 narrateur|Il y a une pomme coupée.
+maman|Tu veux un morceau de pomme ?
+enfant-f|Oui.
 narrateur|Mila s'assoit.
-maman|Tu es bien assise. Bravo.
+maman|Tu es bien assise.
+maman|Bravo.
 narrateur|Elle mange du pain.
+narrateur|Elle croque la pomme.
+narrateur|La pomme est croquante.
+maman|Elle est sucrée, la pomme ?
+enfant-f|Oui.
+enfant-f|Un peu.
 narrateur|Elle boit du lait.
 papa|Tu as fini ton bol ?
 enfant-f|Oui, papa.
-papa|Bravo. L'étape est finie.</t>
+papa|Bravo.
+papa|L'étape est finie.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1752,7 +1771,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Ensuite, le sac. Le sac rose est près de la chaise. Mila met la gourde. Elle met le cahier. Elle met le doudou rouge. Tu as mis ce que maman a dit. Le doudou est dans le sac. Bravo. Tu as fait du bon travail. Mila met les chaussures. Maman ouvre la porte. On est prêtes. Oui. Tu as enchaîné le matin. Une étape après l'autre.</t>
+          <t>Ensuite, le sac. Le sac rose est près de la chaise. Mila met la gourde. Elle met le cahier. Elle met le doudou rouge. Tu as mis ce que maman a dit. Le doudou est dans le sac. Bravo. Tu as fait du bon travail. Mila met les chaussures. Le doudou est bien dans le sac ? Oui, papa. Maman ouvre la porte. On est prêtes. Oui. Tu as enchaîné le matin. Une étape après l'autre.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1895,11 +1914,15 @@
 narrateur|Elle met le doudou rouge.
 papa|Tu as mis ce que maman a dit.
 enfant-f|Le doudou est dans le sac.
-maman|Bravo. Tu as fait du bon travail.
+maman|Bravo.
+maman|Tu as fait du bon travail.
 narrateur|Mila met les chaussures.
+papa|Le doudou est bien dans le sac ?
+enfant-f|Oui, papa.
 narrateur|Maman ouvre la porte.
 enfant-f|On est prêtes.
-maman|Oui. Tu as enchaîné le matin.
+maman|Oui.
+maman|Tu as enchaîné le matin.
 papa|Une étape après l'autre.</t>
         </is>
       </c>
@@ -2100,7 +2123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2143,6 +2166,41 @@
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>

--- a/stories/arbres/ATOM-AUT.ROU.001-06.xlsx
+++ b/stories/arbres/ATOM-AUT.ROU.001-06.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>maison, le matin</t>
+          <t>chambre petite, cuisine, promenade du matin</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bénédicte, maman, papa</t>
+          <t>Mila, papa, maman</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Le doudou rouge attend sur la chaise. Mila se prépare, une étape après l'autre, pour le mettre dans le sac.</t>
+          <t>Mila veut sortir tout de suite avec le doudou rouge. La porte est fermée. Une étape après l'autre, une oreille dépasse du sac, et ils marchent.</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sur la chaise, un doudou rouge attend. Il a deux oreilles toutes molles. Il a un nez en fil. Une oreille penche un peu. L'autre oreille est droite. La chambre de Mila est petite. Les murs sont couleur pêche. Un mobile tourne très lentement. Papa et maman sont dans la maison. Mila, tu vois le doudou ? Oui, maman. Il attend. Il t'attend pour le sac. En ce moment, Mila ouvre les yeux. Le drap est chaud. Ça sent le doudou. Je veux le doudou. D'abord on se lève. Le doudou t'attend pour le sac. Mila regarde la chaise. Le doudou ne bouge pas. On se lève. Une étape après l'autre. Mila se lève. Ses pieds touchent le tapis. Le tapis est doux. Bravo. Tu es debout. Tu as fait l'étape dite. Ensuite, on s'habille. Le pull rose est sur le lit. Mila met le pull. Elle met le pantalon. Elle met les chaussettes. C'est fait. Bravo, Mila. Tu as fait du bon travail.</t>
+          <t>Sur la chaise, un doudou rouge attend. Il a deux oreilles toutes molles. Une oreille penche un peu. L'autre oreille est droite. Le nez est un fil tout doux. Les murs sont couleur pêche. Un mobile tourne très lentement. Une étoile de bois passe, puis un oiseau. Ça fait un tout petit vent. Mila, tu vois le doudou ? Oui, maman. Il attend. Il t'attend pour la promenade. En ce moment, Mila ouvre les yeux. Ça sent le doudou, tout près. Je le prends. Mila prend le doudou. Elle va vers la porte. Elle est encore en pyjama. La porte est fermée. On sort. Oui. Le doudou viendra dans le sac. D'abord le matin. Une étape après l'autre. Mila serre une oreille molle. L'oreille est chaude contre sa joue. On se lève. Mila pose le doudou sur la chaise. Ses pieds touchent le tapis. Le tapis est doux.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1326,41 +1326,35 @@
         <is>
           <t>narrateur|Sur la chaise, un doudou rouge attend.
 narrateur|Il a deux oreilles toutes molles.
-narrateur|Il a un nez en fil.
 narrateur|Une oreille penche un peu.
 narrateur|L'autre oreille est droite.
-narrateur|La chambre de Mila est petite.
+narrateur|Le nez est un fil tout doux.
 narrateur|Les murs sont couleur pêche.
 narrateur|Un mobile tourne très lentement.
-narrateur|Papa et maman sont dans la maison.
+narrateur|Une étoile de bois passe, puis un oiseau.
+narrateur|Ça fait un tout petit vent.
 maman|Mila, tu vois le doudou ?
 enfant-f|Oui, maman.
 enfant-f|Il attend.
-papa|Il t'attend pour le sac.
+papa|Il t'attend pour la promenade.
 narrateur|En ce moment, Mila ouvre les yeux.
-narrateur|Le drap est chaud.
-narrateur|Ça sent le doudou.
-enfant-f|Je veux le doudou.
-maman|D'abord on se lève.
-maman|Le doudou t'attend pour le sac.
-narrateur|Mila regarde la chaise.
-narrateur|Le doudou ne bouge pas.
-papa|On se lève.
+narrateur|Ça sent le doudou, tout près.
+enfant-f|Je le prends.
+narrateur|Mila prend le doudou.
+narrateur|Elle va vers la porte.
+narrateur|Elle est encore en pyjama.
+narrateur|La porte est fermée.
+enfant-f|On sort.
+maman|Oui.
+maman|Le doudou viendra dans le sac.
+papa|D'abord le matin.
 papa|Une étape après l'autre.
-narrateur|Mila se lève.
+narrateur|Mila serre une oreille molle.
+narrateur|L'oreille est chaude contre sa joue.
+maman|On se lève.
+narrateur|Mila pose le doudou sur la chaise.
 narrateur|Ses pieds touchent le tapis.
-narrateur|Le tapis est doux.
-maman|Bravo.
-maman|Tu es debout.
-maman|Tu as fait l'étape dite.
-papa|Ensuite, on s'habille.
-narrateur|Le pull rose est sur le lit.
-narrateur|Mila met le pull.
-narrateur|Elle met le pantalon.
-narrateur|Elle met les chaussettes.
-enfant-f|C'est fait.
-papa|Bravo, Mila.
-papa|Tu as fait du bon travail.</t>
+narrateur|Le tapis est doux.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1392,7 +1386,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Mila se prépare. Comment avance-t-elle ?</t>
+          <t>Mila veut le doudou. Comment avance-t-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1412,7 +1406,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>une étape | après l'autre | étape | les étapes</t>
+          <t>une étape | après l'autre | étape | les étapes | une étape après l'autre</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1427,7 +1421,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Elle fait une étape après l'autre. Comment avance Bénédicte ?</t>
+          <t>Elle fait une étape après l'autre. Comment avance Mila ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1548,11 +1542,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Mila se prépare.
+          <t>narrateur|Mila veut le doudou.
 narrateur|Comment avance-t-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1577,7 +1570,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Mila a fait l'étape dite. Une étape après l'autre. Maintenant, le déjeuner. Mila va à la cuisine. La table est ronde. Il y a du pain. Il y a une pomme coupée. Tu veux un morceau de pomme ? Oui. Mila s'assoit. Tu es bien assise. Bravo. Elle mange du pain. Elle croque la pomme. La pomme est croquante. Elle est sucrée, la pomme ? Oui. Un peu. Elle boit du lait. Tu as fini ton bol ? Oui, papa. Bravo. L'étape est finie.</t>
+          <t>Une étape après l'autre. Le pull rose, sur le lit. Mila enfile le pull. Le pull est doux, un peu épais. C'est fait. Ensuite, la pomme. Mila va à la cuisine. La table est ronde. Il y a du pain. Il y a une pomme coupée. Tu veux un morceau de pomme ? Oui. Mila s'assoit. Elle croque la pomme. La pomme est croquante. Elle est sucrée ? Un peu. Le doudou t'attend encore.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1721,9 +1714,12 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Mila a fait l'étape dite.
-maman|Une étape après l'autre.
-papa|Maintenant, le déjeuner.
+          <t>maman|Une étape après l'autre.
+papa|Le pull rose, sur le lit.
+narrateur|Mila enfile le pull.
+narrateur|Le pull est doux, un peu épais.
+enfant-f|C'est fait.
+maman|Ensuite, la pomme.
 narrateur|Mila va à la cuisine.
 narrateur|La table est ronde.
 narrateur|Il y a du pain.
@@ -1731,22 +1727,13 @@
 maman|Tu veux un morceau de pomme ?
 enfant-f|Oui.
 narrateur|Mila s'assoit.
-maman|Tu es bien assise.
-maman|Bravo.
-narrateur|Elle mange du pain.
 narrateur|Elle croque la pomme.
 narrateur|La pomme est croquante.
-maman|Elle est sucrée, la pomme ?
-enfant-f|Oui.
+maman|Elle est sucrée ?
 enfant-f|Un peu.
-narrateur|Elle boit du lait.
-papa|Tu as fini ton bol ?
-enfant-f|Oui, papa.
-papa|Bravo.
-papa|L'étape est finie.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+papa|Le doudou t'attend encore.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1771,7 +1758,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Ensuite, le sac. Le sac rose est près de la chaise. Mila met la gourde. Elle met le cahier. Elle met le doudou rouge. Tu as mis ce que maman a dit. Le doudou est dans le sac. Bravo. Tu as fait du bon travail. Mila met les chaussures. Le doudou est bien dans le sac ? Oui, papa. Maman ouvre la porte. On est prêtes. Oui. Tu as enchaîné le matin. Une étape après l'autre.</t>
+          <t>Ensuite, le sac. Le sac rose est près de la chaise. Mila met la gourde. Elle met le cahier. Elle met le doudou rouge. Une oreille dépasse. C'est bien. Il voit la promenade. Mila met ses chaussures. Le doudou est dans le sac ? Oui, papa. Maman ouvre la porte. L'air sent les feuilles. On est prêtes. Oui. L'oreille rouge bouge un peu. Mila pose la main dessus. Le poil est un peu usé, tout doux. Il marche avec nous.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1912,18 +1899,20 @@
 narrateur|Mila met la gourde.
 narrateur|Elle met le cahier.
 narrateur|Elle met le doudou rouge.
-papa|Tu as mis ce que maman a dit.
-enfant-f|Le doudou est dans le sac.
-maman|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|Mila met les chaussures.
-papa|Le doudou est bien dans le sac ?
+enfant-f|Une oreille dépasse.
+papa|C'est bien.
+papa|Il voit la promenade.
+narrateur|Mila met ses chaussures.
+papa|Le doudou est dans le sac ?
 enfant-f|Oui, papa.
 narrateur|Maman ouvre la porte.
+narrateur|L'air sent les feuilles.
 enfant-f|On est prêtes.
 maman|Oui.
-maman|Tu as enchaîné le matin.
-papa|Une étape après l'autre.</t>
+narrateur|L'oreille rouge bouge un peu.
+narrateur|Mila pose la main dessus.
+narrateur|Le poil est un peu usé, tout doux.
+papa|Il marche avec nous.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1955,7 +1944,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Je me suis levée. Je me suis habillée. J'ai déjeuné. J'ai mis le doudou. Bravo, Mila. Le doudou n'a plus besoin d'attendre. L'histoire est finie.</t>
+          <t>Le doudou n'attend plus. Il marche avec toi. Une étape après l'autre. Le mobile, derrière, tourne encore. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2095,16 +2084,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-f|Je me suis levée.
-enfant-f|Je me suis habillée.
-enfant-f|J'ai déjeuné.
-enfant-f|J'ai mis le doudou.
-maman|Bravo, Mila.
-papa|Le doudou n'a plus besoin d'attendre.
+          <t>enfant-f|Le doudou n'attend plus.
+maman|Il marche avec toi.
+papa|Une étape après l'autre.
+narrateur|Le mobile, derrière, tourne encore.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2123,7 +2109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2203,6 +2189,13 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.ROU.001-06.xlsx
+++ b/stories/arbres/ATOM-AUT.ROU.001-06.xlsx
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mila veut sortir tout de suite avec le doudou rouge. La porte est fermée. Une étape après l'autre, une oreille dépasse du sac, et ils marchent.</t>
+          <t>Mila veut sortir tout de suite avec le doudou rouge. La porte est fermée. Une chose puis la suivante, une oreille dépasse du sac, et ils marchent.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sur la chaise, un doudou rouge attend. Il a deux oreilles toutes molles. Une oreille penche un peu. L'autre oreille est droite. Le nez est un fil tout doux. Les murs sont couleur pêche. Un mobile tourne très lentement. Une étoile de bois passe, puis un oiseau. Ça fait un tout petit vent. Mila, tu vois le doudou ? Oui, maman. Il attend. Il t'attend pour la promenade. En ce moment, Mila ouvre les yeux. Ça sent le doudou, tout près. Je le prends. Mila prend le doudou. Elle va vers la porte. Elle est encore en pyjama. La porte est fermée. On sort. Oui. Le doudou viendra dans le sac. D'abord le matin. Une étape après l'autre. Mila serre une oreille molle. L'oreille est chaude contre sa joue. On se lève. Mila pose le doudou sur la chaise. Ses pieds touchent le tapis. Le tapis est doux.</t>
+          <t>Sur la chaise, un doudou rouge attend. Il a deux oreilles toutes molles. Une oreille penche un peu. L'autre oreille est droite. Le nez est un fil tout doux. Les murs sont couleur pêche. Un mobile tourne très lentement. Une étoile de bois passe, puis un oiseau. Ça fait un tout petit vent. Mila, tu vois le doudou ? Oui, maman. Il attend. Il t'attend pour la promenade. En ce moment, Mila ouvre les yeux. Ça sent le doudou, tout près. Je le prends. Mila prend le doudou. Elle va vers la porte. Elle est encore en pyjama. La porte est fermée. On sort. Oui. Le doudou viendra dans le sac. D'abord le matin. Une chose, puis la suivante. Mila serre une oreille molle. L'oreille est chaude contre sa joue. On se lève ? Oui. Mila pose le doudou sur la chaise. Ses pieds touchent le tapis. Le tapis est doux. Le pull, maintenant.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le matin, Bénédicte ouvre les yeux. Maman dit : &lt;emphasis level="moderate"&gt;une&lt;/emphasis&gt; étape après l'autre. D'abord, Bénédicte se lève. Ses pieds touchent le tapis. Ensuite, elle s'habille. Elle met le pull. Elle met le pantalon. Papa dit : maintenant, le déjeuner. Bénédicte s'assoit. Elle mange du pain. Elle boit du lait. Maman dit : ensuite, le sac. Bénédicte met la gourde. Elle met le cahier. Une étape après l'autre. Bénédicte est prête.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sur la chaise, un doudou rouge attend. Il a deux oreilles toutes molles. Une oreille penche un peu. L'autre oreille est droite. Le nez est un fil tout doux. Les murs sont couleur pêche. Un mobile tourne très lentement. Une étoile de bois passe, puis un oiseau. Ça fait un tout petit vent. Mila, tu vois le doudou ? Oui, maman. Il attend. Il t'attend pour la promenade. En ce moment, Mila ouvre les yeux. Ça sent le doudou, tout près. Je le prends. Mila prend le doudou. Elle va vers la porte. Elle est encore en pyjama. La porte est fermée. On sort. Oui. Le doudou viendra dans le sac. D'abord le matin. Une chose, puis la suivante. Mila serre une oreille molle. L'oreille est chaude contre sa joue. On se lève ? Oui. Mila pose le doudou sur la chaise. Ses pieds touchent le tapis. Le tapis est doux. Le pull, maintenant.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1245,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1348,13 +1348,15 @@
 maman|Oui.
 maman|Le doudou viendra dans le sac.
 papa|D'abord le matin.
-papa|Une étape après l'autre.
+papa|Une chose, puis la suivante.
 narrateur|Mila serre une oreille molle.
 narrateur|L'oreille est chaude contre sa joue.
-maman|On se lève.
+maman|On se lève ?
+enfant-f|Oui.
 narrateur|Mila pose le doudou sur la chaise.
 narrateur|Ses pieds touchent le tapis.
-narrateur|Le tapis est doux.</t>
+narrateur|Le tapis est doux.
+maman|Le pull, maintenant.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1386,12 +1388,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Mila veut le doudou. Comment avance-t-elle ?</t>
+          <t>Mila veut la promenade. Comment se prépare-t-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Bénédicte se prépare. Comment avance-t-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila veut la promenade. Comment se prépare-t-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1401,12 +1403,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>une étape</t>
+          <t>une chose</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>une étape | après l'autre | étape | les étapes | une étape après l'autre</t>
+          <t>une chose | puis l'autre | d'abord | doucement | une chose puis l'autre | puis la suivante</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1421,7 +1423,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Elle fait une étape après l'autre. Comment avance Mila ?</t>
+          <t>Elle fait une chose, puis la suivante. Comment se prépare Mila ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1470,7 +1472,7 @@
         <v>0.8</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1542,8 +1544,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Mila veut le doudou.
-narrateur|Comment avance-t-elle ?</t>
+          <t>narrateur|Mila veut la promenade.
+narrateur|Comment se prépare-t-elle ?</t>
         </is>
       </c>
     </row>
@@ -1570,12 +1572,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Une étape après l'autre. Le pull rose, sur le lit. Mila enfile le pull. Le pull est doux, un peu épais. C'est fait. Ensuite, la pomme. Mila va à la cuisine. La table est ronde. Il y a du pain. Il y a une pomme coupée. Tu veux un morceau de pomme ? Oui. Mila s'assoit. Elle croque la pomme. La pomme est croquante. Elle est sucrée ? Un peu. Le doudou t'attend encore.</t>
+          <t>Le pull rose est sur le dossier. Mila enfile le pull. Le coton est un peu tiède. C'est fait. Ensuite, le bol. Mila va à la cuisine. Le carrelage est froid. Ça sent le lait. Tu veux le bol rouge ? Oui, le rouge. Elle s'assoit. Elle boit une gorgée. Le lait est tiède. Le doudou t'attend sur la chaise. Après, dans le sac. Merci, Mila.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Bénédicte a fait l'étape dite. Se lever. S'habiller. Déje&lt;emphasis level="moderate"&gt;une&lt;/emphasis&gt;r. Le sac. Une étape après l'autre.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le pull rose est sur le dossier. Mila enfile le pull. Le coton est un peu tiède. C'est fait. Ensuite, le bol. Mila va à la cuisine. Le carrelage est froid. Ça sent le lait. Tu veux le bol rouge ? Oui, le rouge. Elle s'assoit. Elle boit une gorgée. Le lait est tiède. Le doudou t'attend sur la chaise. Après, dans le sac. Merci, Mila.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1631,14 +1633,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1714,24 +1716,22 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>maman|Une étape après l'autre.
-papa|Le pull rose, sur le lit.
+          <t>narrateur|Le pull rose est sur le dossier.
 narrateur|Mila enfile le pull.
-narrateur|Le pull est doux, un peu épais.
+narrateur|Le coton est un peu tiède.
 enfant-f|C'est fait.
-maman|Ensuite, la pomme.
+papa|Ensuite, le bol.
 narrateur|Mila va à la cuisine.
-narrateur|La table est ronde.
-narrateur|Il y a du pain.
-narrateur|Il y a une pomme coupée.
-maman|Tu veux un morceau de pomme ?
-enfant-f|Oui.
-narrateur|Mila s'assoit.
-narrateur|Elle croque la pomme.
-narrateur|La pomme est croquante.
-maman|Elle est sucrée ?
-enfant-f|Un peu.
-papa|Le doudou t'attend encore.</t>
+narrateur|Le carrelage est froid.
+narrateur|Ça sent le lait.
+maman|Tu veux le bol rouge ?
+enfant-f|Oui, le rouge.
+narrateur|Elle s'assoit.
+narrateur|Elle boit une gorgée.
+narrateur|Le lait est tiède.
+papa|Le doudou t'attend sur la chaise.
+enfant-f|Après, dans le sac.
+maman|Merci, Mila.</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Ensuite, le sac. Le sac rose est près de la chaise. Mila met la gourde. Elle met le cahier. Elle met le doudou rouge. Une oreille dépasse. C'est bien. Il voit la promenade. Mila met ses chaussures. Le doudou est dans le sac ? Oui, papa. Maman ouvre la porte. L'air sent les feuilles. On est prêtes. Oui. L'oreille rouge bouge un peu. Mila pose la main dessus. Le poil est un peu usé, tout doux. Il marche avec nous.</t>
+          <t>Ensuite, le sac. Le sac jaune est près de la porte. Mila met la gourde. Elle glisse le doudou. Une oreille dépasse un peu. Tu as mis le doudou ? Oui, papa. Mila met ses chaussures. Le bon pied ? Oui. Papa ouvre la porte. L'air du matin entre, frais. Le chemin sent l'herbe coupée. Ils marchent, tout doux. Le sac tape contre la hanche. L'oreille dépasse. Elle voit la promenade. Toi aussi. Une feuille sèche roule sur le chemin. On continue ? Oui, encore un peu. Mila serre la sangle. Le doudou chauffe contre son dos. Le mobile, derrière eux, ne tourne plus. Le chemin sent encore l'herbe. Tu es sortie, tout doucement ? Oui, une chose, puis l'autre.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Bénédicte met les chaussures. Maman ouvre la porte.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Ensuite, le sac. Le sac jaune est près de la porte. Mila met la gourde. Elle glisse le doudou. Une oreille dépasse un peu. Tu as mis le doudou ? Oui, papa. Mila met ses chaussures. Le bon pied ? Oui. Papa ouvre la porte. L'air du matin entre, frais. Le chemin sent l'herbe coupée. Ils marchent, tout doux. Le sac tape contre la hanche. L'oreille dépasse. Elle voit la promenade. Toi aussi. Une feuille sèche roule sur le chemin. On continue ? Oui, encore un peu. Mila serre la sangle. Le doudou chauffe contre son dos. Le mobile, derrière eux, ne tourne plus. Le chemin sent encore l'herbe. Tu es sortie, tout doucement ? Oui, une chose, puis l'autre.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1819,14 +1819,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1895,24 +1895,32 @@
       <c r="AW5" t="inlineStr">
         <is>
           <t>maman|Ensuite, le sac.
-narrateur|Le sac rose est près de la chaise.
+narrateur|Le sac jaune est près de la porte.
 narrateur|Mila met la gourde.
-narrateur|Elle met le cahier.
-narrateur|Elle met le doudou rouge.
-enfant-f|Une oreille dépasse.
-papa|C'est bien.
-papa|Il voit la promenade.
+narrateur|Elle glisse le doudou.
+narrateur|Une oreille dépasse un peu.
+papa|Tu as mis le doudou ?
+enfant-f|Oui, papa.
 narrateur|Mila met ses chaussures.
-papa|Le doudou est dans le sac ?
-enfant-f|Oui, papa.
-narrateur|Maman ouvre la porte.
-narrateur|L'air sent les feuilles.
-enfant-f|On est prêtes.
-maman|Oui.
-narrateur|L'oreille rouge bouge un peu.
-narrateur|Mila pose la main dessus.
-narrateur|Le poil est un peu usé, tout doux.
-papa|Il marche avec nous.</t>
+maman|Le bon pied ?
+enfant-f|Oui.
+narrateur|Papa ouvre la porte.
+narrateur|L'air du matin entre, frais.
+narrateur|Le chemin sent l'herbe coupée.
+narrateur|Ils marchent, tout doux.
+narrateur|Le sac tape contre la hanche.
+enfant-f|L'oreille dépasse.
+maman|Elle voit la promenade.
+papa|Toi aussi.
+narrateur|Une feuille sèche roule sur le chemin.
+enfant-f|On continue ?
+maman|Oui, encore un peu.
+narrateur|Mila serre la sangle.
+narrateur|Le doudou chauffe contre son dos.
+narrateur|Le mobile, derrière eux, ne tourne plus.
+narrateur|Le chemin sent encore l'herbe.
+maman|Tu es sortie, tout doucement ?
+enfant-f|Oui, une chose, puis l'autre.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1944,12 +1952,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le doudou n'attend plus. Il marche avec toi. Une étape après l'autre. Le mobile, derrière, tourne encore. L'histoire est finie.</t>
+          <t>On est dehors. Une chose, puis la suivante. Le doudou a fait le chemin avec toi. L'oreille rouge dépasse encore. Bravo, Mila. L'air frais reste sur ses joues.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>On est dehors. Une chose, puis la suivante. Le doudou a fait le chemin avec toi. L'oreille rouge dépasse encore. Bravo, Mila. L'air frais reste sur ses joues.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2005,14 +2013,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.82</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2084,11 +2092,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-f|Le doudou n'attend plus.
-maman|Il marche avec toi.
-papa|Une étape après l'autre.
-narrateur|Le mobile, derrière, tourne encore.
-narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On est dehors.
+papa|Une chose, puis la suivante.
+maman|Le doudou a fait le chemin avec toi.
+narrateur|L'oreille rouge dépasse encore.
+papa|Bravo, Mila.
+narrateur|L'air frais reste sur ses joues.</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2194,6 +2203,13 @@
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-AUT.ROU.001-06.xlsx
+++ b/stories/arbres/ATOM-AUT.ROU.001-06.xlsx
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mila veut sortir tout de suite avec le doudou rouge. La porte est fermée. Une chose puis la suivante, une oreille dépasse du sac, et ils marchent.</t>
+          <t>Au nid du mobile, un éclat de promenade brille sur l'oreille. Mila veut le chemin, maintenant. La porte reste fermée. Elle prend tout d'un coup : le sac bascule, le doudou roule. Elle refuse de foncer, pose le doudou, le pull, le bol. Au sac, la gourde et le doudou se coincent. Elle retrouve l'éclat. Dehors, l'éclat de promenade tient sur l'oreille.</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sur la chaise, un doudou rouge attend. Il a deux oreilles toutes molles. Une oreille penche un peu. L'autre oreille est droite. Le nez est un fil tout doux. Les murs sont couleur pêche. Un mobile tourne très lentement. Une étoile de bois passe, puis un oiseau. Ça fait un tout petit vent. Mila, tu vois le doudou ? Oui, maman. Il attend. Il t'attend pour la promenade. En ce moment, Mila ouvre les yeux. Ça sent le doudou, tout près. Je le prends. Mila prend le doudou. Elle va vers la porte. Elle est encore en pyjama. La porte est fermée. On sort. Oui. Le doudou viendra dans le sac. D'abord le matin. Une chose, puis la suivante. Mila serre une oreille molle. L'oreille est chaude contre sa joue. On se lève ? Oui. Mila pose le doudou sur la chaise. Ses pieds touchent le tapis. Le tapis est doux. Le pull, maintenant.</t>
+          <t>Une étoile de bois glisse sur le mur. Le mur est couleur pêche. Un oiseau de bois la suit. Ça fait un vent minuscule. Au nid du mobile, ça sent le coton. Il tourne, papa. Oui, le mobile tourne. Sur la chaise, le doudou rouge attend. Une oreille penche, molle. L'autre oreille reste droite. Sur l'oreille molle, un éclat de promenade brille. C'est un éclat de promenade. Il est petit, comme un chemin. Il brille vers la porte. Le nez du doudou est un fil. Le fil est rouge, un peu rêche. On sort, maintenant ! Mila veut la promenade, maintenant. Le drap du lit sent le savon. En ce moment, elle saisit le doudou. Elle court vers la porte. Le pyjama frotte ses genoux. La porte reste fermée. Derrière la porte, l'air sent l'herbe. Ouvre, papa ! Elle tire la poignée, les deux mains. Le doudou glisse, tombe. Une oreille se plie sous la chaise. Oh. Le sourire de Mila disparaît. Dans sa poitrine, envie et inquiétude se bousculent. Je prends tout, d'un coup ! Elle prend le sac, une chaussure, le doudou. Le sac bascule. La chaussure tape le tapis. Le doudou roule sous la chaise. Ça ne veut pas. Ses épaules tombent un peu. Papa se baisse à sa hauteur. Tu cherches l'éclat, Mila ? Il est sous la chaise. On se prépare, Mila ? Je veux le chemin.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Sur la chaise, un doudou rouge attend. Il a deux oreilles toutes molles. Une oreille penche un peu. L'autre oreille est droite. Le nez est un fil tout doux. Les murs sont couleur pêche. Un mobile tourne très lentement. Une étoile de bois passe, puis un oiseau. Ça fait un tout petit vent. Mila, tu vois le doudou ? Oui, maman. Il attend. Il t'attend pour la promenade. En ce moment, Mila ouvre les yeux. Ça sent le doudou, tout près. Je le prends. Mila prend le doudou. Elle va vers la porte. Elle est encore en pyjama. La porte est fermée. On sort. Oui. Le doudou viendra dans le sac. D'abord le matin. Une chose, puis la suivante. Mila serre une oreille molle. L'oreille est chaude contre sa joue. On se lève ? Oui. Mila pose le doudou sur la chaise. Ses pieds touchent le tapis. Le tapis est doux. Le pull, maintenant.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Une étoile de bois glisse sur le mur. Le mur est couleur pêche. Un oiseau de bois la suit. Ça fait un vent minuscule. Au nid du mobile, ça sent le coton. Il tourne, papa. Oui, le mobile tourne. Sur la chaise, le doudou rouge attend. Une oreille penche, molle. L'autre oreille reste droite. Sur l'oreille molle, un &lt;emphasis level="moderate"&gt;éclat de promenade&lt;/emphasis&gt; brille. C'est un éclat de promenade. Il est petit, comme un chemin. Il brille vers la porte. Le nez du doudou est un fil. Le fil est rouge, un peu rêche. On sort, maintenant ! Mila veut la promenade, maintenant. Le drap du lit sent le savon. En ce moment, elle saisit le doudou. Elle court vers la porte. Le pyjama frotte ses genoux. La porte reste fermée. Derrière la porte, l'air sent l'herbe. Ouvre, papa ! Elle tire la poignée, les deux mains. Le doudou glisse, tombe. Une oreille se plie sous la chaise. Oh. Le sourire de Mila disparaît. Dans sa poitrine, envie et inquiétude se bousculent. Je prends tout, d'un coup ! Elle prend le sac, une chaussure, le doudou. Le sac bascule. La chaussure tape le tapis. Le doudou roule sous la chaise. Ça ne veut pas. Ses épaules tombent un peu. Papa se baisse à sa hauteur. Tu cherches l'éclat, Mila ? Il est sous la chaise. On se prépare, Mila ? Je veux le chemin.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Le matin, Bénédicte ouvre les yeux. Maman dit : &lt;emphasis&gt;une&lt;/emphasis&gt; étape après l'autre. D'abord, Bénédicte se lève. Ses pieds touchent le tapis. Ensuite, elle s'habille. Elle met le pull. Elle met le pantalon. Papa dit : maintenant, le déjeuner. Bénédicte s'assoit. Elle mange du pain. Elle boit du lait. Maman dit : ensuite, le sac. Bénédicte met la gourde. Elle met le cahier. Une étape après l'autre. Bénédicte est prête.&lt;/slow&gt; [pause]</t>
+          <t>Une étoile de bois glisse sur le mur. Le mur est couleur pêche. Un oiseau de bois la suit. Ça fait un vent minuscule. Au nid du mobile, ça sent le coton. Il tourne, papa. Oui, le mobile tourne. Sur la chaise, le doudou rouge attend. Une oreille penche, molle. L'autre oreille reste droite. Sur l'oreille molle, un &lt;emphasis&gt;éclat de promenade&lt;/emphasis&gt; brille. C'est un éclat de promenade. Il est petit, comme un chemin. Il brille vers la porte. Le nez du doudou est un fil. Le fil est rouge, un peu rêche. On sort, maintenant ! Mila veut la promenade, maintenant. Le drap du lit sent le savon. En ce moment, elle saisit le doudou. Elle court vers la porte. Le pyjama frotte ses genoux. La porte reste fermée. Derrière la porte, l'air sent l'herbe. Ouvre, papa ! Elle tire la poignée, les deux mains. Le doudou glisse, tombe. Une oreille se plie sous la chaise. Oh. Le sourire de Mila disparaît. Dans sa poitrine, envie et inquiétude se bousculent. Je prends tout, d'un coup ! Elle prend le sac, une chaussure, le doudou. Le sac bascule. La chaussure tape le tapis. Le doudou roule sous la chaise. Ça ne veut pas. Ses épaules tombent un peu. Papa se baisse à sa hauteur. Tu cherches l'éclat, Mila ? Il est sous la chaise. On se prépare, Mila ? Je veux le chemin. [pause]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>0.86</v>
+        <v>0.98</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1275,30 +1275,30 @@
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>une</t>
+          <t>éclat de promenade</t>
         </is>
       </c>
       <c r="AI2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" s="2" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AK2" s="2" t="n">
-        <v>380</v>
+        <v>260</v>
       </c>
       <c r="AL2" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="AM2" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>storytelling</t>
         </is>
       </c>
       <c r="AN2" s="2" t="n">
-        <v>0.333</v>
+        <v>0.36</v>
       </c>
       <c r="AO2" s="2" t="inlineStr"/>
       <c r="AP2" s="2" t="inlineStr">
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="AQ2" s="2" t="n">
-        <v>0.86</v>
+        <v>0.98</v>
       </c>
       <c r="AR2" s="2" t="n">
-        <v>0.86</v>
+        <v>0.98</v>
       </c>
       <c r="AS2" s="2" t="n">
         <v>100</v>
@@ -1319,49 +1319,63 @@
         <v>50</v>
       </c>
       <c r="AU2" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AV2" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="AV2" s="2" t="inlineStr">
+        <is>
+          <t>arc=installation; intention=émerveiller puis tendre; emotion=impatience puis découragement; intensite=2; destinataire=enfant; sous_texte=elle_veut_le_chemin_maintenant; tempo=naturel puis resserré; sourire=léger puis aucun; respiration=ample puis retenue</t>
+        </is>
+      </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Sur la chaise, un doudou rouge attend.
-narrateur|Il a deux oreilles toutes molles.
-narrateur|Une oreille penche un peu.
-narrateur|L'autre oreille est droite.
-narrateur|Le nez est un fil tout doux.
-narrateur|Les murs sont couleur pêche.
-narrateur|Un mobile tourne très lentement.
-narrateur|Une étoile de bois passe, puis un oiseau.
-narrateur|Ça fait un tout petit vent.
-maman|Mila, tu vois le doudou ?
-enfant-f|Oui, maman.
-enfant-f|Il attend.
-papa|Il t'attend pour la promenade.
-narrateur|En ce moment, Mila ouvre les yeux.
-narrateur|Ça sent le doudou, tout près.
-enfant-f|Je le prends.
-narrateur|Mila prend le doudou.
-narrateur|Elle va vers la porte.
-narrateur|Elle est encore en pyjama.
-narrateur|La porte est fermée.
-enfant-f|On sort.
-maman|Oui.
-maman|Le doudou viendra dans le sac.
-papa|D'abord le matin.
-papa|Une chose, puis la suivante.
-narrateur|Mila serre une oreille molle.
-narrateur|L'oreille est chaude contre sa joue.
-maman|On se lève ?
-enfant-f|Oui.
-narrateur|Mila pose le doudou sur la chaise.
-narrateur|Ses pieds touchent le tapis.
-narrateur|Le tapis est doux.
-maman|Le pull, maintenant.</t>
+          <t>narrateur|Une étoile de bois glisse sur le mur.
+narrateur|Le mur est couleur pêche.
+narrateur|Un oiseau de bois la suit.
+narrateur|Ça fait un vent minuscule.
+narrateur|Au nid du mobile, ça sent le coton.
+enfant-f|Il tourne, papa.
+papa|Oui, le mobile tourne.
+narrateur|Sur la chaise, le doudou rouge attend.
+narrateur|Une oreille penche, molle.
+narrateur|L'autre oreille reste droite.
+narrateur|Sur l'oreille molle, un éclat de promenade brille.
+papa|C'est un éclat de promenade.
+enfant-f|Il est petit, comme un chemin.
+maman|Il brille vers la porte.
+narrateur|Le nez du doudou est un fil.
+narrateur|Le fil est rouge, un peu rêche.
+enfant-f|On sort, maintenant !
+narrateur|Mila veut la promenade, maintenant.
+narrateur|Le drap du lit sent le savon.
+narrateur|En ce moment, elle saisit le doudou.
+narrateur|Elle court vers la porte.
+narrateur|Le pyjama frotte ses genoux.
+narrateur|La porte reste fermée.
+narrateur|Derrière la porte, l'air sent l'herbe.
+enfant-f|Ouvre, papa !
+narrateur|Elle tire la poignée, les deux mains.
+narrateur|Le doudou glisse, tombe.
+narrateur|Une oreille se plie sous la chaise.
+enfant-f|Oh.
+narrateur|Le sourire de Mila disparaît.
+narrateur|Dans sa poitrine, envie et inquiétude se bousculent.
+enfant-f|Je prends tout, d'un coup !
+narrateur|Elle prend le sac, une chaussure, le doudou.
+narrateur|Le sac bascule.
+narrateur|La chaussure tape le tapis.
+narrateur|Le doudou roule sous la chaise.
+enfant-f|Ça ne veut pas.
+narrateur|Ses épaules tombent un peu.
+narrateur|Papa se baisse à sa hauteur.
+papa|Tu cherches l'éclat, Mila ?
+enfant-f|Il est sous la chaise.
+maman|On se prépare, Mila ?
+enfant-f|Je veux le chemin.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>doudou</t>
+          <t>mobile,doudou</t>
         </is>
       </c>
     </row>
@@ -1393,12 +1407,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Mila veut la promenade. Comment se prépare-t-elle ?</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Mila veut la &lt;emphasis level="moderate"&gt;promenade&lt;/emphasis&gt;. Comment se prépare-t-elle ?&lt;/prosody&gt;&lt;break time="700ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Bénédicte se prépare. Comment avance-t-elle ?&lt;/slow&gt;</t>
+          <t>&lt;soft&gt;&lt;slow&gt;Mila veut la &lt;emphasis&gt;promenade&lt;/emphasis&gt;. Comment se prépare-t-elle ?&lt;/slow&gt;&lt;/soft&gt; [pause]</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -1461,7 +1475,7 @@
         </is>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1469,10 +1483,10 @@
         </is>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1487,34 +1501,38 @@
       <c r="AE3" s="2" t="inlineStr"/>
       <c r="AF3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>soft</t>
         </is>
       </c>
       <c r="AG3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" s="2" t="inlineStr"/>
+        <v>-2</v>
+      </c>
+      <c r="AH3" s="2" t="inlineStr">
+        <is>
+          <t>promenade</t>
+        </is>
+      </c>
       <c r="AI3" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ3" s="2" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AK3" s="2" t="n">
-        <v>380</v>
+        <v>320</v>
       </c>
       <c r="AL3" s="2" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>focused</t>
         </is>
       </c>
       <c r="AM3" s="2" t="inlineStr">
         <is>
-          <t>rise</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AN3" s="2" t="n">
-        <v>0.333</v>
+        <v>0.32</v>
       </c>
       <c r="AO3" s="2" t="inlineStr"/>
       <c r="AP3" s="2" t="inlineStr">
@@ -1523,13 +1541,13 @@
         </is>
       </c>
       <c r="AQ3" s="2" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="AR3" s="2" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="AS3" s="2" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="AT3" s="2" t="n">
         <v>50</v>
@@ -1539,7 +1557,7 @@
       </c>
       <c r="AV3" s="2" t="inlineStr">
         <is>
-          <t>question d'écoute, ne change pas le cours</t>
+          <t>arc=indice; intention=faire_deviner; emotion=attention; intensite=1; destinataire=enfant; sous_texte=une_chose_puis_le_doudou_peut_venir; tempo=suspendu; sourire=aucun; respiration=courte_avant_question</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -1572,17 +1590,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Le pull rose est sur le dossier. Mila enfile le pull. Le coton est un peu tiède. C'est fait. Ensuite, le bol. Mila va à la cuisine. Le carrelage est froid. Ça sent le lait. Tu veux le bol rouge ? Oui, le rouge. Elle s'assoit. Elle boit une gorgée. Le lait est tiède. Le doudou t'attend sur la chaise. Après, dans le sac. Merci, Mila.</t>
+          <t>Mila pose le sac près du lit. La chaussure aussi. Elle pose un genou au tapis. Sous la chaise, le doudou attend. Je le sors toute seule. Elle tire l'oreille, trop vite. L'oreille se plie, de travers. Oh. Mila ne reprend pas trop vite. Elle écoute la chambre, un instant. Le mobile tourne, petit. Sur l'oreille, l'éclat de promenade brille. Il est là. Mila refuse de foncer. Elle glisse le doudou, lente. Le doudou sent le coton chaud. Sur la chaise. Elle le pose, bien droit. Le pull, Mila ? Oui, maman. Le pull rose est sur le dossier. Mila enfile le pull. Le coton est un peu tiède. C'est fait. Ensuite, le bol ? Mila va à la cuisine. Le carrelage est froid sous ses pieds. Ça sent le lait. À la fenêtre, une lumière ronde. Tu veux le bol rouge ? Oui, le rouge. Elle s'assoit. Le bol est lisse, un peu lourd. Elle boit une gorgée. Le lait est tiède. Le doudou t'attend sur la chaise. Après, dans le sac. Merci, Mila. Il vient avec nous.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Le pull rose est sur le dossier. Mila enfile le pull. Le coton est un peu tiède. C'est fait. Ensuite, le bol. Mila va à la cuisine. Le carrelage est froid. Ça sent le lait. Tu veux le bol rouge ? Oui, le rouge. Elle s'assoit. Elle boit une gorgée. Le lait est tiède. Le doudou t'attend sur la chaise. Après, dans le sac. Merci, Mila.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Mila pose le sac près du lit. La chaussure aussi. Elle pose un genou au tapis. Sous la chaise, le &lt;emphasis level="moderate"&gt;doudou&lt;/emphasis&gt; attend. Je le sors toute seule. Elle tire l'oreille, trop vite. L'oreille se plie, de travers. Oh. Mila ne reprend pas trop vite. Elle écoute la chambre, un instant. Le mobile tourne, petit. Sur l'oreille, l'éclat de promenade brille. Il est là. Mila refuse de foncer. Elle glisse le doudou, lente. Le doudou sent le coton chaud. Sur la chaise. Elle le pose, bien droit. Le pull, Mila ? Oui, maman. Le pull rose est sur le dossier. Mila enfile le pull. Le coton est un peu tiède. C'est fait. Ensuite, le bol ? Mila va à la cuisine. Le carrelage est froid sous ses pieds. Ça sent le lait. À la fenêtre, une lumière ronde. Tu veux le bol rouge ? Oui, le rouge. Elle s'assoit. Le bol est lisse, un peu lourd. Elle boit une gorgée. Le lait est tiède. Le doudou t'attend sur la chaise. Après, dans le sac. Merci, Mila. Il vient avec nous.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Bénédicte a fait l'étape dite. Se lever. S'habiller. Déje&lt;emphasis&gt;une&lt;/emphasis&gt;r. Le sac. Une étape après l'autre.&lt;/slow&gt; [pause]</t>
+          <t>Mila pose le sac près du lit. La chaussure aussi. Elle pose un genou au tapis. Sous la chaise, le &lt;emphasis&gt;doudou&lt;/emphasis&gt; attend. Je le sors toute seule. Elle tire l'oreille, trop vite. L'oreille se plie, de travers. Oh. Mila ne reprend pas trop vite. Elle écoute la chambre, un instant. Le mobile tourne, petit. Sur l'oreille, l'éclat de promenade brille. Il est là. Mila refuse de foncer. Elle glisse le doudou, lente. Le doudou sent le coton chaud. Sur la chaise. Elle le pose, bien droit. Le pull, Mila ? Oui, maman. Le pull rose est sur le dossier. Mila enfile le pull. Le coton est un peu tiède. C'est fait. Ensuite, le bol ? Mila va à la cuisine. Le carrelage est froid sous ses pieds. Ça sent le lait. À la fenêtre, une lumière ronde. Tu veux le bol rouge ? Oui, le rouge. Elle s'assoit. Le bol est lisse, un peu lourd. Elle boit une gorgée. Le lait est tiède. Le doudou t'attend sur la chaise. Après, dans le sac. Merci, Mila. Il vient avec nous. [pause]</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -1629,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
@@ -1637,10 +1655,10 @@
         </is>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0.86</v>
+        <v>0.97</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1663,30 +1681,30 @@
       </c>
       <c r="AH4" s="2" t="inlineStr">
         <is>
-          <t>une</t>
+          <t>doudou</t>
         </is>
       </c>
       <c r="AI4" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ4" s="2" t="n">
-        <v>450</v>
+        <v>560</v>
       </c>
       <c r="AK4" s="2" t="n">
-        <v>380</v>
+        <v>270</v>
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>bright</t>
         </is>
       </c>
       <c r="AM4" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN4" s="2" t="n">
-        <v>0.333</v>
+        <v>0.35</v>
       </c>
       <c r="AO4" s="2" t="inlineStr"/>
       <c r="AP4" s="2" t="inlineStr">
@@ -1695,10 +1713,10 @@
         </is>
       </c>
       <c r="AQ4" s="2" t="n">
-        <v>0.86</v>
+        <v>0.97</v>
       </c>
       <c r="AR4" s="2" t="n">
-        <v>0.86</v>
+        <v>0.97</v>
       </c>
       <c r="AS4" s="2" t="n">
         <v>100</v>
@@ -1707,31 +1725,59 @@
         <v>50</v>
       </c>
       <c r="AU4" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr">
         <is>
-          <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
+          <t>arc=résolution; intention=faire_vivre_le_geste; emotion=concentration puis fierté_calme; intensite=2; destinataire=enfant; sous_texte=elle_pose_le_doudou_sans_foncer; tempo=naturel; sourire=léger; respiration=relâchée</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Le pull rose est sur le dossier.
+          <t>narrateur|Mila pose le sac près du lit.
+narrateur|La chaussure aussi.
+narrateur|Elle pose un genou au tapis.
+narrateur|Sous la chaise, le doudou attend.
+enfant-f|Je le sors toute seule.
+narrateur|Elle tire l'oreille, trop vite.
+narrateur|L'oreille se plie, de travers.
+enfant-f|Oh.
+narrateur|Mila ne reprend pas trop vite.
+narrateur|Elle écoute la chambre, un instant.
+narrateur|Le mobile tourne, petit.
+narrateur|Sur l'oreille, l'éclat de promenade brille.
+enfant-f|Il est là.
+narrateur|Mila refuse de foncer.
+narrateur|Elle glisse le doudou, lente.
+narrateur|Le doudou sent le coton chaud.
+enfant-f|Sur la chaise.
+narrateur|Elle le pose, bien droit.
+maman|Le pull, Mila ?
+enfant-f|Oui, maman.
+narrateur|Le pull rose est sur le dossier.
 narrateur|Mila enfile le pull.
 narrateur|Le coton est un peu tiède.
 enfant-f|C'est fait.
-papa|Ensuite, le bol.
+papa|Ensuite, le bol ?
 narrateur|Mila va à la cuisine.
-narrateur|Le carrelage est froid.
+narrateur|Le carrelage est froid sous ses pieds.
 narrateur|Ça sent le lait.
+narrateur|À la fenêtre, une lumière ronde.
 maman|Tu veux le bol rouge ?
 enfant-f|Oui, le rouge.
 narrateur|Elle s'assoit.
+narrateur|Le bol est lisse, un peu lourd.
 narrateur|Elle boit une gorgée.
 narrateur|Le lait est tiède.
 papa|Le doudou t'attend sur la chaise.
 enfant-f|Après, dans le sac.
-maman|Merci, Mila.</t>
+papa|Merci, Mila.
+enfant-f|Il vient avec nous.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>bol,lait</t>
         </is>
       </c>
     </row>
@@ -1758,17 +1804,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Ensuite, le sac. Le sac jaune est près de la porte. Mila met la gourde. Elle glisse le doudou. Une oreille dépasse un peu. Tu as mis le doudou ? Oui, papa. Mila met ses chaussures. Le bon pied ? Oui. Papa ouvre la porte. L'air du matin entre, frais. Le chemin sent l'herbe coupée. Ils marchent, tout doux. Le sac tape contre la hanche. L'oreille dépasse. Elle voit la promenade. Toi aussi. Une feuille sèche roule sur le chemin. On continue ? Oui, encore un peu. Mila serre la sangle. Le doudou chauffe contre son dos. Le mobile, derrière eux, ne tourne plus. Le chemin sent encore l'herbe. Tu es sortie, tout doucement ? Oui, une chose, puis l'autre.</t>
+          <t>Le sac, maintenant ? Le sac jaune est près de la porte. Une sangle pend, un peu rêche. Mila veut tout mettre, d'un coup. Elle pousse le doudou et la gourde. La gourde roule. Le doudou se coince, de travers. Il ne rentre pas ! Mila veut foncer, d'un coup. Mila refuse de foncer. Ses épaules se serrent un peu. Ça tape, dans sa poitrine. Personne ne dit la suite. Elle regarde le doudou. Elle écoute le nid du mobile. Le mobile fait un vent minuscule. Sur l'oreille, l'éclat de promenade brille. Comme sur la chaise ! Tu le vois, toi ? Oui, sur cette oreille. Mila pose la gourde, d'abord. Toc, au fond du sac. Puis elle glisse le doudou. L'oreille dépasse, avec l'éclat. Il voit le chemin. Mila met ses chaussures. Le bon pied ? Oui. Papa ouvre la porte. L'air du matin entre, frais. Le chemin sent l'herbe coupée.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Ensuite, le sac. Le sac jaune est près de la porte. Mila met la gourde. Elle glisse le doudou. Une oreille dépasse un peu. Tu as mis le doudou ? Oui, papa. Mila met ses chaussures. Le bon pied ? Oui. Papa ouvre la porte. L'air du matin entre, frais. Le chemin sent l'herbe coupée. Ils marchent, tout doux. Le sac tape contre la hanche. L'oreille dépasse. Elle voit la promenade. Toi aussi. Une feuille sèche roule sur le chemin. On continue ? Oui, encore un peu. Mila serre la sangle. Le doudou chauffe contre son dos. Le mobile, derrière eux, ne tourne plus. Le chemin sent encore l'herbe. Tu es sortie, tout doucement ? Oui, une chose, puis l'autre.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Le sac, maintenant ? Le sac jaune est près de la porte. Une sangle pend, un peu rêche. Mila veut tout mettre, d'un coup. Elle pousse le doudou et la gourde. La gourde roule. Le doudou se coince, de travers. Il ne rentre pas ! Mila veut foncer, d'un coup. Mila refuse de foncer. Ses épaules se serrent un peu. Ça tape, dans sa poitrine. Personne ne dit la suite. Elle regarde le doudou. Elle écoute le nid du mobile. Le mobile fait un vent minuscule. Sur l'oreille, l'&lt;emphasis level="moderate"&gt;éclat de promenade&lt;/emphasis&gt; brille. Comme sur la chaise ! Tu le vois, toi ? Oui, sur cette oreille. Mila pose la gourde, d'abord. Toc, au fond du sac. Puis elle glisse le doudou. L'oreille dépasse, avec l'éclat. Il voit le chemin. Mila met ses chaussures. Le bon pied ? Oui. Papa ouvre la porte. L'air du matin entre, frais. Le chemin sent l'herbe coupée.&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Bénédicte met les chaussures. Maman ouvre la porte.&lt;/slow&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;Le sac, maintenant ? Le sac jaune est près de la porte. Une sangle pend, un peu rêche. Mila veut tout mettre, d'un coup. Elle pousse le doudou et la gourde. La gourde roule. Le doudou se coince, de travers. Il ne rentre pas ! Mila veut foncer, d'un coup. Mila refuse de foncer. Ses épaules se serrent un peu. Ça tape, dans sa poitrine. Personne ne dit la suite. Elle regarde le doudou. Elle écoute le nid du mobile. Le mobile fait un vent minuscule. Sur l'oreille, l'&lt;emphasis&gt;éclat de promenade&lt;/emphasis&gt; brille. Comme sur la chaise ! Tu le vois, toi ? Oui, sur cette oreille. Mila pose la gourde, d'abord. Toc, au fond du sac. Puis elle glisse le doudou. L'oreille dépasse, avec l'éclat. Il voit le chemin. Mila met ses chaussures. Le bon pied ? Oui. Papa ouvre la porte. L'air du matin entre, frais. Le chemin sent l'herbe coupée.&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -1815,7 +1861,7 @@
         </is>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
@@ -1823,22 +1869,26 @@
         </is>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="AE5" s="2" t="inlineStr"/>
+          <t>-2st</t>
+        </is>
+      </c>
+      <c r="AE5" s="2" t="inlineStr">
+        <is>
+          <t>low-pitch</t>
+        </is>
+      </c>
       <c r="AF5" s="2" t="inlineStr">
         <is>
           <t>medium</t>
@@ -1847,28 +1897,32 @@
       <c r="AG5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AH5" s="2" t="inlineStr"/>
+      <c r="AH5" s="2" t="inlineStr">
+        <is>
+          <t>éclat de promenade</t>
+        </is>
+      </c>
       <c r="AI5" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ5" s="2" t="n">
-        <v>450</v>
+        <v>520</v>
       </c>
       <c r="AK5" s="2" t="n">
-        <v>380</v>
+        <v>300</v>
       </c>
       <c r="AL5" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>tense</t>
         </is>
       </c>
       <c r="AM5" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="AN5" s="2" t="n">
-        <v>0.333</v>
+        <v>0.34</v>
       </c>
       <c r="AO5" s="2" t="inlineStr"/>
       <c r="AP5" s="2" t="inlineStr">
@@ -1877,55 +1931,63 @@
         </is>
       </c>
       <c r="AQ5" s="2" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="AR5" s="2" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="AS5" s="2" t="n">
         <v>100</v>
       </c>
       <c r="AT5" s="2" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AU5" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AV5" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="AV5" s="2" t="inlineStr">
+        <is>
+          <t>arc=obstacle; intention=alerter_sans_effrayer; emotion=élan puis prudence; intensite=2; destinataire=enfant; sous_texte=elle_refuse_de_foncer_retrouve_l_eclat; tempo=resserré; sourire=aucun; respiration=retenue</t>
+        </is>
+      </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>maman|Ensuite, le sac.
+          <t>maman|Le sac, maintenant ?
 narrateur|Le sac jaune est près de la porte.
-narrateur|Mila met la gourde.
-narrateur|Elle glisse le doudou.
-narrateur|Une oreille dépasse un peu.
-papa|Tu as mis le doudou ?
-enfant-f|Oui, papa.
+narrateur|Une sangle pend, un peu rêche.
+narrateur|Mila veut tout mettre, d'un coup.
+narrateur|Elle pousse le doudou et la gourde.
+narrateur|La gourde roule.
+narrateur|Le doudou se coince, de travers.
+enfant-f|Il ne rentre pas !
+narrateur|Mila veut foncer, d'un coup.
+narrateur|Mila refuse de foncer.
+narrateur|Ses épaules se serrent un peu.
+narrateur|Ça tape, dans sa poitrine.
+narrateur|Personne ne dit la suite.
+narrateur|Elle regarde le doudou.
+narrateur|Elle écoute le nid du mobile.
+narrateur|Le mobile fait un vent minuscule.
+narrateur|Sur l'oreille, l'éclat de promenade brille.
+enfant-f|Comme sur la chaise !
+papa|Tu le vois, toi ?
+enfant-f|Oui, sur cette oreille.
+narrateur|Mila pose la gourde, d'abord.
+narrateur|Toc, au fond du sac.
+narrateur|Puis elle glisse le doudou.
+narrateur|L'oreille dépasse, avec l'éclat.
+enfant-f|Il voit le chemin.
 narrateur|Mila met ses chaussures.
 maman|Le bon pied ?
 enfant-f|Oui.
 narrateur|Papa ouvre la porte.
 narrateur|L'air du matin entre, frais.
-narrateur|Le chemin sent l'herbe coupée.
-narrateur|Ils marchent, tout doux.
-narrateur|Le sac tape contre la hanche.
-enfant-f|L'oreille dépasse.
-maman|Elle voit la promenade.
-papa|Toi aussi.
-narrateur|Une feuille sèche roule sur le chemin.
-enfant-f|On continue ?
-maman|Oui, encore un peu.
-narrateur|Mila serre la sangle.
-narrateur|Le doudou chauffe contre son dos.
-narrateur|Le mobile, derrière eux, ne tourne plus.
-narrateur|Le chemin sent encore l'herbe.
-maman|Tu es sortie, tout doucement ?
-enfant-f|Oui, une chose, puis l'autre.</t>
+narrateur|Le chemin sent l'herbe coupée.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>porte</t>
+          <t>sac,porte</t>
         </is>
       </c>
     </row>
@@ -1952,17 +2014,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>On est dehors. Une chose, puis la suivante. Le doudou a fait le chemin avec toi. L'oreille rouge dépasse encore. Bravo, Mila. L'air frais reste sur ses joues.</t>
+          <t>Ils marchent sur le chemin de l'herbe. Le sac tape contre la hanche. L'oreille dépasse. Elle voit la promenade ? Oui, maman. L'éclat de promenade brille, dehors. Comme dans la chambre ! Tu le vois sur l'oreille ? Oui, papa. Une feuille sèche roule sur le chemin. Mila serre la sangle. Le doudou chauffe contre son dos. Le sac ne voulait pas. Et là, il vient avec nous. Le mobile, derrière eux, ne tourne plus. Un coin de l'oreille porte une trace d'herbe. Une petite herbe, papa. L'air frais reste sur ses joues. L'éclat de promenade tient sur l'oreille.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>On est dehors. Une chose, puis la suivante. Le doudou a fait le chemin avec toi. L'oreille rouge dépasse encore. Bravo, Mila. L'air frais reste sur ses joues.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Ils marchent sur le chemin de l'herbe. Le sac tape contre la hanche. L'oreille dépasse. Elle voit la promenade ? Oui, maman. L'&lt;emphasis level="moderate"&gt;éclat de promenade&lt;/emphasis&gt; brille, dehors. Comme dans la chambre ! Tu le vois sur l'oreille ? Oui, papa. Une feuille sèche roule sur le chemin. Mila serre la sangle. Le doudou chauffe contre son dos. Le sac ne voulait pas. Et là, il vient avec nous. Le mobile, derrière eux, ne tourne plus. Un coin de l'oreille porte une trace d'herbe. Une petite herbe, papa. L'air frais reste sur ses joues. L'éclat de promenade tient sur l'oreille.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Ils marchent sur le chemin de l'herbe. Le sac tape contre la hanche. L'oreille dépasse. Elle voit la promenade ? Oui, maman. L'&lt;emphasis&gt;éclat de promenade&lt;/emphasis&gt; brille, dehors. Comme dans la chambre ! Tu le vois sur l'oreille ? Oui, papa. Une feuille sèche roule sur le chemin. Mila serre la sangle. Le doudou chauffe contre son dos. Le sac ne voulait pas. Et là, il vient avec nous. Le mobile, derrière eux, ne tourne plus. Un coin de l'oreille porte une trace d'herbe. Une petite herbe, papa. L'air frais reste sur ses joues. L'éclat de promenade tient sur l'oreille.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -2009,18 +2071,18 @@
         </is>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2029,12 +2091,12 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>-2st</t>
         </is>
       </c>
       <c r="AE6" s="2" t="inlineStr">
         <is>
-          <t>lower-pitch</t>
+          <t>low-pitch</t>
         </is>
       </c>
       <c r="AF6" s="2" t="inlineStr">
@@ -2043,17 +2105,21 @@
         </is>
       </c>
       <c r="AG6" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AH6" s="2" t="inlineStr"/>
+        <v>-3</v>
+      </c>
+      <c r="AH6" s="2" t="inlineStr">
+        <is>
+          <t>éclat de promenade</t>
+        </is>
+      </c>
       <c r="AI6" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="AK6" s="2" t="n">
-        <v>380</v>
+        <v>340</v>
       </c>
       <c r="AL6" s="2" t="inlineStr">
         <is>
@@ -2062,11 +2128,11 @@
       </c>
       <c r="AM6" s="2" t="inlineStr">
         <is>
-          <t>fall</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.333</v>
+        <v>0.31</v>
       </c>
       <c r="AO6" s="2" t="inlineStr"/>
       <c r="AP6" s="2" t="inlineStr">
@@ -2075,29 +2141,51 @@
         </is>
       </c>
       <c r="AQ6" s="2" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="AR6" s="2" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="AS6" s="2" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AT6" s="2" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="AU6" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AV6" s="2" t="inlineStr">
+        <is>
+          <t>arc=retour; intention=refermer; emotion=tendresse et fierté_calme; intensite=1; destinataire=enfant; sous_texte=l_eclat_du_debut_tient_sur_l_oreille; tempo=posé; sourire=léger; respiration=ample</t>
+        </is>
+      </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-f|On est dehors.
-papa|Une chose, puis la suivante.
-maman|Le doudou a fait le chemin avec toi.
-narrateur|L'oreille rouge dépasse encore.
-papa|Bravo, Mila.
-narrateur|L'air frais reste sur ses joues.</t>
+          <t>narrateur|Ils marchent sur le chemin de l'herbe.
+narrateur|Le sac tape contre la hanche.
+enfant-f|L'oreille dépasse.
+maman|Elle voit la promenade ?
+enfant-f|Oui, maman.
+narrateur|L'éclat de promenade brille, dehors.
+enfant-f|Comme dans la chambre !
+papa|Tu le vois sur l'oreille ?
+enfant-f|Oui, papa.
+narrateur|Une feuille sèche roule sur le chemin.
+narrateur|Mila serre la sangle.
+narrateur|Le doudou chauffe contre son dos.
+enfant-f|Le sac ne voulait pas.
+maman|Et là, il vient avec nous.
+narrateur|Le mobile, derrière eux, ne tourne plus.
+narrateur|Un coin de l'oreille porte une trace d'herbe.
+enfant-f|Une petite herbe, papa.
+narrateur|L'air frais reste sur ses joues.
+narrateur|L'éclat de promenade tient sur l'oreille.</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>herbe,chemin</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2210,6 +2298,13 @@
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
